--- a/outputs/evaluation/decision/v2/CF_M01/run_2/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_2/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8571</v>
+        <v>0.8333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8571</v>
+        <v>0.7143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.858</v>
+        <v>0.9021</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
         <v>0.9519</v>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8571</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,28 +755,28 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
         <v>9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -792,28 +792,28 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -829,19 +829,19 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7883</v>
+        <v>0.8202</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1003,86 +1003,84 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9471000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be processed in the analytical module, improving the scalability and availability of the system.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: Increasing the security of the system by reducing the entry points to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_03, C_04, Scalability</t>
+          <t>C_05, Security</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_12, AU_16, AU_18, AU_19, AU_20, AU_21</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42, 44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C07</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8289</v>
+        <v>0.8413</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1096,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1108,66 +1106,68 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams is used to transmit playlog and audit trail data to ensure the fastest possible data transmission, allowing for near real-time transmission.</t>
+          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>C_03, C_04, Scalability</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_12, AU_16, AU_18, AU_19, AU_20, AU_21</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_C01</t>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8398</v>
+        <v>0.9228</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1187,45 +1187,45 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8603</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. It increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>It is the set of cloud computing services that allows the creation of scalable and highly available applications. The use of AWS was decided and not other cloud services due to its low price and its previous use by the company.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>C_02, C_04</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>*CF_M01_C07</t>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8477</v>
+        <v>0.9373</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>NestJS allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1316,28 +1316,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD05</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8893</v>
+        <v>0.9886</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8603</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>AWS was chosen over other cloud services due to its low price and its previous use by the company, allowing the creation of scalable and highly available applications.</t>
+          <t>The use of this language was decided, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1381,105 +1381,20 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
+          <t>*CF_M01_C11</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M01_AD05</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9542</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>TypeScript was chosen over JavaScript because it is the default language for NestJS and because its static typing allows for error detection at compile time.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>CF_M01_AU34</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1542,12 +1457,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazon Athena is a serverless service that makes it unnecessary to manage infrastructure when there is an increase in the data set and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
+          <t>This service, being a serverless service, means that it is not necessary to manage the infrastructure when there is an increase in the set of data and users.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>C_03, Scalability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1562,11 +1477,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6716</v>
+        <v>0.6661</v>
       </c>
     </row>
   </sheetData>
@@ -1580,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1650,7 +1565,38 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6038</v>
+        <v>0.6364</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6771</v>
       </c>
     </row>
   </sheetData>
